--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\t\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E209DB15-D4D8-4A5F-BF3A-1D3BC833DBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C0F119-2F75-43FF-ADAE-FF88A268E631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,11 @@
     <sheet name="sorting" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -800,9 +805,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1206,22 +1210,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1434,7 +1438,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1444,7 +1448,7 @@
       <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>110</v>
       </c>
       <c r="E2" t="s">
@@ -1550,7 +1554,7 @@
       <c r="E7" t="s">
         <v>83</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1816,7 +1820,7 @@
         <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1838,7 +1842,7 @@
         <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -2046,6 +2050,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2787,40 +2792,40 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="2"/>
-    <col min="2" max="2" width="33.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.21875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="17.77734375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="21.21875" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="33.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.21875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>155</v>
       </c>
       <c r="C2" t="s">
@@ -2832,15 +2837,15 @@
       <c r="E2" t="s">
         <v>122</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>151</v>
       </c>
       <c r="C3" t="s">
@@ -2852,15 +2857,15 @@
       <c r="E3" t="s">
         <v>128</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>156</v>
       </c>
       <c r="C4" t="s">
@@ -2872,15 +2877,15 @@
       <c r="E4" t="s">
         <v>121</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>152</v>
       </c>
       <c r="C5" t="s">
@@ -2892,87 +2897,87 @@
       <c r="E5" t="s">
         <v>127</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>103</v>
       </c>
       <c r="D6" t="s">
         <v>124</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>119</v>
       </c>
       <c r="D7" t="s">
         <v>146</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="1" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="1" t="s">
         <v>103</v>
       </c>
     </row>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C0F119-2F75-43FF-ADAE-FF88A268E631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92962AAB-A084-4AEA-A484-33C9B0605176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
@@ -761,7 +761,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>cloze</t>
+    <t>seaHard</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92962AAB-A084-4AEA-A484-33C9B0605176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61037793-7FAF-413B-BED0-02AA07C9B84D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\廖雨潔\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5DBFBB-346C-4892-A504-1675DD48D5FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9704D77-94E5-4985-8D2C-28A17B3E3EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="201">
   <si>
     <t>activeScence</t>
   </si>
@@ -758,6 +758,10 @@
   </si>
   <si>
     <t>eat seaweed as</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sorting</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1149,7 +1153,7 @@
         <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>200</v>
       </c>
       <c r="D2" t="s">
         <v>105</v>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\廖雨潔\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B0C421-92D7-4E20-B63F-1B4F3E8A28AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529988B9-E522-43DC-AC5D-3ADF36E404EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\廖雨潔\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B0C421-92D7-4E20-B63F-1B4F3E8A28AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBBFD527-A796-4039-984D-CEC25809C22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBBFD527-A796-4039-984D-CEC25809C22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B50577F-6314-4A8B-8DC5-AAC3E740A9FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="203">
   <si>
     <t>activeScence</t>
   </si>
@@ -766,6 +766,10 @@
   </si>
   <si>
     <t>sorting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seaHard</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1157,7 +1161,7 @@
         <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>202</v>
       </c>
       <c r="D2" t="s">
         <v>105</v>
@@ -1171,7 +1175,7 @@
         <v>107</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D3" t="s">
         <v>106</v>
@@ -1185,7 +1189,7 @@
         <v>108</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="D4" t="s">
         <v>109</v>
@@ -1199,7 +1203,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
         <v>105</v>
@@ -1213,7 +1217,7 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
         <v>106</v>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\廖雨潔\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B50577F-6314-4A8B-8DC5-AAC3E740A9FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF3F2F2-1F4F-4303-94C1-2BFA900B54A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1161,7 +1161,7 @@
         <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D2" t="s">
         <v>105</v>
@@ -1189,7 +1189,7 @@
         <v>108</v>
       </c>
       <c r="C4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D4" t="s">
         <v>109</v>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\廖雨潔\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF3F2F2-1F4F-4303-94C1-2BFA900B54A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4461511-4A29-4A6E-A4B3-0A4672B2662B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="196">
   <si>
     <t>activeScence</t>
   </si>
@@ -140,18 +140,9 @@
     <t>recycling</t>
   </si>
   <si>
-    <t>多吃蔬果</t>
-  </si>
-  <si>
-    <t>eat more fruits and vegetables</t>
-  </si>
-  <si>
     <t>public transportation</t>
   </si>
   <si>
-    <t>環保餐具</t>
-  </si>
-  <si>
     <t>reusable container</t>
   </si>
   <si>
@@ -161,12 +152,6 @@
     <t>turn off lights when leaving</t>
   </si>
   <si>
-    <t>reduce single-use plastics </t>
-  </si>
-  <si>
-    <t>省水裝置</t>
-  </si>
-  <si>
     <t>water-saving devices</t>
   </si>
   <si>
@@ -308,14 +293,6 @@
   </si>
   <si>
     <t>節約用電</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大眾運輸工具</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>避免使用塑膠袋</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -769,7 +746,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>seaHard</t>
+    <t>Hard</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1141,7 +1118,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1158,13 +1135,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1172,13 +1149,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1186,13 +1163,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1203,10 +1180,10 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1217,10 +1194,10 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1247,13 +1224,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>28</v>
@@ -1270,16 +1247,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1287,16 +1264,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D3" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="F3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1304,16 +1281,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D4" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E4" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="F4" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1321,16 +1298,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D5" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="E5" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F5" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1338,16 +1315,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D6" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="E6" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F6" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1355,16 +1332,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D7" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="E7" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="F7" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1372,16 +1349,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D8" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E8" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="F8" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1389,16 +1366,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D9" t="s">
+        <v>181</v>
+      </c>
+      <c r="E9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F9" t="s">
         <v>188</v>
-      </c>
-      <c r="E9" t="s">
-        <v>189</v>
-      </c>
-      <c r="F9" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1406,16 +1383,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D10" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="E10" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F10" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1423,16 +1400,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D11" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="E11" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F11" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -1456,7 +1433,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B1" t="s">
         <v>8</v>
@@ -1485,13 +1462,13 @@
         <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1502,16 +1479,16 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="F3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1522,16 +1499,16 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="F4" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1542,10 +1519,10 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
         <v>15</v>
@@ -1562,7 +1539,7 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
@@ -1588,7 +1565,7 @@
         <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>18</v>
@@ -1611,7 +1588,7 @@
         <v>20</v>
       </c>
       <c r="F8" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1625,10 +1602,10 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F9" t="s">
         <v>14</v>
@@ -1642,7 +1619,7 @@
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
         <v>23</v>
@@ -1662,7 +1639,7 @@
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
         <v>15</v>
@@ -1694,7 +1671,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B1" t="s">
         <v>26</v>
@@ -1717,19 +1694,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="F2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1737,19 +1714,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="F3" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1757,19 +1734,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E4" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1777,19 +1754,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E5" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F5" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1797,19 +1774,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F6" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -1830,7 +1807,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B1" t="s">
         <v>26</v>
@@ -1853,10 +1830,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1864,10 +1841,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1875,10 +1852,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1886,10 +1863,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1897,10 +1874,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1908,10 +1885,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1919,10 +1896,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1930,10 +1907,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1941,10 +1918,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1966,13 +1943,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B1" t="s">
         <v>26</v>
       </c>
       <c r="C1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D1" t="s">
         <v>28</v>
@@ -1989,10 +1966,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -2000,10 +1977,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -2011,10 +1988,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C4" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -2022,10 +1999,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C5" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -2033,10 +2010,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C6" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -2044,10 +2021,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C7" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -2055,10 +2032,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C8" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -2066,10 +2043,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -2077,10 +2054,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C10" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2092,7 +2069,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.44140625" customWidth="1"/>
@@ -2102,13 +2079,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B1" t="s">
         <v>26</v>
       </c>
       <c r="C1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D1" t="s">
         <v>28</v>
@@ -2125,7 +2102,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
         <v>31</v>
@@ -2147,10 +2124,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -2158,10 +2135,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -2169,65 +2146,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
         <v>42</v>
-      </c>
-      <c r="C9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2235,7 +2157,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="B3:F4 B1 D1:F1 C2:F2 B6:F7 C5:F5 B9:F11 C8:F8" numberStoredAsText="1"/>
+    <ignoredError sqref="B3:F3 B1 D1:F1 C2:F2 B4:F4 B5:F6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2250,7 +2172,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B1" t="s">
         <v>26</v>
@@ -2273,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -2284,10 +2206,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -2295,10 +2217,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -2306,10 +2228,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -2317,10 +2239,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" t="s">
         <v>48</v>
-      </c>
-      <c r="C6" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -2328,10 +2250,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -2339,10 +2261,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -2350,10 +2272,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -2361,10 +2283,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -2372,10 +2294,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -2383,10 +2305,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -2394,10 +2316,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
         <v>55</v>
-      </c>
-      <c r="C13" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -2405,10 +2327,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -2416,10 +2338,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -2427,10 +2349,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -2456,7 +2378,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B1" t="s">
         <v>26</v>
@@ -2479,19 +2401,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -2499,19 +2421,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" t="s">
         <v>64</v>
       </c>
-      <c r="C3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" t="s">
-        <v>69</v>
-      </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -2519,19 +2441,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
         <v>33</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -2539,19 +2461,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
         <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -2559,19 +2481,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="D6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" t="s">
-        <v>45</v>
-      </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -2579,19 +2501,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -2599,19 +2521,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -2619,19 +2541,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
         <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -2639,19 +2561,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
         <v>64</v>
       </c>
-      <c r="C10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" t="s">
-        <v>69</v>
-      </c>
       <c r="E10" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -2659,19 +2581,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F11" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -2679,19 +2601,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
         <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -2699,19 +2621,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E13" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -2719,19 +2641,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" t="s">
         <v>64</v>
       </c>
-      <c r="C14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" t="s">
-        <v>69</v>
-      </c>
       <c r="E14" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F14" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -2739,19 +2661,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" t="s">
         <v>64</v>
       </c>
-      <c r="C15" t="s">
-        <v>69</v>
-      </c>
       <c r="D15" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E15" t="s">
         <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -2759,19 +2681,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" t="s">
         <v>40</v>
       </c>
-      <c r="D16" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" t="s">
-        <v>45</v>
-      </c>
       <c r="F16" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -2779,19 +2701,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E17" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F17" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -2799,19 +2721,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F18" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2839,13 +2761,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>28</v>
@@ -2862,19 +2784,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E2" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2882,19 +2804,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="D3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
@@ -2902,19 +2824,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C4" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E4" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2922,19 +2844,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C5" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2942,19 +2864,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2962,19 +2884,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2982,19 +2904,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -3002,19 +2924,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\廖雨潔\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4461511-4A29-4A6E-A4B3-0A4672B2662B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85509BF0-CADD-412D-814F-6E529E82DADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -746,7 +746,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Hard</t>
+    <t>hard</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85509BF0-CADD-412D-814F-6E529E82DADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A602DDBE-D38F-4541-9579-4B92529AF079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1138,7 +1138,7 @@
         <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>194</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
         <v>98</v>
@@ -1180,7 +1180,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>194</v>
       </c>
       <c r="D5" t="s">
         <v>98</v>
@@ -1194,7 +1194,7 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
         <v>99</v>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A602DDBE-D38F-4541-9579-4B92529AF079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A388BD0-5E0D-4780-98FF-15D78D766FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1138,7 +1138,7 @@
         <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>193</v>
       </c>
       <c r="D2" t="s">
         <v>98</v>
@@ -1152,7 +1152,7 @@
         <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>193</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
         <v>99</v>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A388BD0-5E0D-4780-98FF-15D78D766FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A2AD52-7FC4-494D-ABED-CC5D65FA293B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1152,7 +1152,7 @@
         <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>195</v>
       </c>
       <c r="D3" t="s">
         <v>99</v>
@@ -1166,7 +1166,7 @@
         <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>195</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
         <v>102</v>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A2AD52-7FC4-494D-ABED-CC5D65FA293B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FAA3BEB-5B48-4843-BFD9-8482EFAF81B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FAA3BEB-5B48-4843-BFD9-8482EFAF81B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{033E95A3-2D98-4856-AF58-CFB8C1409040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
@@ -18,11 +18,11 @@
     <sheet name="seaEasy" sheetId="9" r:id="rId3"/>
     <sheet name="seaNormal" sheetId="8" r:id="rId4"/>
     <sheet name="seaHard" sheetId="10" r:id="rId5"/>
-    <sheet name="hard" sheetId="3" r:id="rId6"/>
-    <sheet name="normal" sheetId="4" r:id="rId7"/>
-    <sheet name="easy" sheetId="5" r:id="rId8"/>
-    <sheet name="cloze" sheetId="7" r:id="rId9"/>
-    <sheet name="sorting" sheetId="11" r:id="rId10"/>
+    <sheet name="easy_match" sheetId="3" r:id="rId6"/>
+    <sheet name="easy_classify" sheetId="4" r:id="rId7"/>
+    <sheet name="easy_card" sheetId="5" r:id="rId8"/>
+    <sheet name="easy_cloze" sheetId="7" r:id="rId9"/>
+    <sheet name="easy_sorting" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="192">
   <si>
     <t>activeScence</t>
   </si>
@@ -134,9 +134,6 @@
     <t>power saving</t>
   </si>
   <si>
-    <t>資源回收</t>
-  </si>
-  <si>
     <t>recycling</t>
   </si>
   <si>
@@ -146,24 +143,15 @@
     <t>reusable container</t>
   </si>
   <si>
-    <t>隨手關燈</t>
-  </si>
-  <si>
     <t>turn off lights when leaving</t>
   </si>
   <si>
     <t>water-saving devices</t>
   </si>
   <si>
-    <t>電動車​</t>
-  </si>
-  <si>
     <t>electric vehicle</t>
   </si>
   <si>
-    <t>共享單車</t>
-  </si>
-  <si>
     <t>bike sharing</t>
   </si>
   <si>
@@ -289,10 +277,6 @@
   </si>
   <si>
     <t>optionA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>節約用電</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -747,6 +731,10 @@
   </si>
   <si>
     <t>hard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>question</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1118,7 +1106,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1135,13 +1123,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1149,13 +1137,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1163,13 +1151,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1180,10 +1168,10 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1194,10 +1182,10 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1224,13 +1212,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>28</v>
@@ -1247,16 +1235,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1264,16 +1252,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1281,16 +1269,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D4" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E4" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="F4" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1298,16 +1286,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1315,16 +1303,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D6" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E6" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1332,16 +1320,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D7" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E7" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F7" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1349,16 +1337,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F8" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1366,16 +1354,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D9" t="s">
+        <v>176</v>
+      </c>
+      <c r="E9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F9" t="s">
         <v>183</v>
-      </c>
-      <c r="D9" t="s">
-        <v>181</v>
-      </c>
-      <c r="E9" t="s">
-        <v>182</v>
-      </c>
-      <c r="F9" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1383,16 +1371,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D10" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E10" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F10" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1400,16 +1388,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D11" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E11" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F11" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -1433,7 +1421,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B1" t="s">
         <v>8</v>
@@ -1462,13 +1450,13 @@
         <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1479,16 +1467,16 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1499,16 +1487,16 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1519,10 +1507,10 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
         <v>15</v>
@@ -1539,7 +1527,7 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
@@ -1565,7 +1553,7 @@
         <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>18</v>
@@ -1588,7 +1576,7 @@
         <v>20</v>
       </c>
       <c r="F8" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1602,10 +1590,10 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F9" t="s">
         <v>14</v>
@@ -1619,7 +1607,7 @@
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
         <v>23</v>
@@ -1639,7 +1627,7 @@
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
         <v>15</v>
@@ -1671,7 +1659,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B1" t="s">
         <v>26</v>
@@ -1694,19 +1682,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1714,19 +1702,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1734,19 +1722,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" t="s">
         <v>116</v>
       </c>
-      <c r="D4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E4" t="s">
-        <v>121</v>
-      </c>
       <c r="F4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1754,19 +1742,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" t="s">
         <v>117</v>
       </c>
-      <c r="D5" t="s">
-        <v>122</v>
-      </c>
       <c r="E5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1774,19 +1762,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F6" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1807,7 +1795,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B1" t="s">
         <v>26</v>
@@ -1830,10 +1818,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1841,10 +1829,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1852,10 +1840,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1863,10 +1851,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1874,10 +1862,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1885,10 +1873,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1896,10 +1884,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1907,10 +1895,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" t="s">
         <v>85</v>
-      </c>
-      <c r="C9" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1918,10 +1906,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1943,13 +1931,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B1" t="s">
         <v>26</v>
       </c>
       <c r="C1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D1" t="s">
         <v>28</v>
@@ -1966,10 +1954,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1977,10 +1965,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1988,10 +1976,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1999,10 +1987,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -2010,10 +1998,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -2021,10 +2009,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C7" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -2032,10 +2020,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C8" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -2043,10 +2031,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C9" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -2054,10 +2042,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C10" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -2069,23 +2057,23 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="22.44140625" customWidth="1"/>
+    <col min="2" max="2" width="63.33203125" customWidth="1"/>
     <col min="3" max="3" width="33.5546875" customWidth="1"/>
     <col min="4" max="4" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>191</v>
       </c>
       <c r="C1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D1" t="s">
         <v>28</v>
@@ -2095,61 +2083,6 @@
       </c>
       <c r="F1" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -2157,7 +2090,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="B3:F3 B1 D1:F1 C2:F2 B4:F4 B5:F6" numberStoredAsText="1"/>
+    <ignoredError sqref="D4:F4 D3:F3 D5:F5 D7:F7 D6 F6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2172,10 +2105,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>191</v>
       </c>
       <c r="C1" t="s">
         <v>27</v>
@@ -2195,10 +2128,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -2206,10 +2139,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -2217,10 +2150,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -2228,10 +2161,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
         <v>43</v>
-      </c>
-      <c r="C5" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -2239,10 +2172,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -2250,10 +2183,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -2261,10 +2194,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -2272,10 +2205,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -2283,10 +2216,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -2294,10 +2227,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -2305,10 +2238,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -2316,10 +2249,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -2327,10 +2260,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -2338,10 +2271,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -2349,17 +2282,17 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="B1:F1 B3:F11 B2 E2:F2 B13:F16 B12 D12:F12" numberStoredAsText="1"/>
+    <ignoredError sqref="C1:F1 B3:F11 B2 E2:F2 B13:F16 B12 D12:F12" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2378,7 +2311,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B1" t="s">
         <v>26</v>
@@ -2401,19 +2334,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" t="s">
         <v>59</v>
-      </c>
-      <c r="C2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -2421,19 +2354,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -2441,19 +2374,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -2461,19 +2394,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
         <v>31</v>
       </c>
       <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
         <v>34</v>
       </c>
-      <c r="E5" t="s">
-        <v>35</v>
-      </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -2481,19 +2414,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
         <v>37</v>
       </c>
-      <c r="D6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" t="s">
-        <v>40</v>
-      </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -2501,19 +2434,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -2521,19 +2454,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -2541,19 +2474,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
         <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -2561,19 +2494,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -2581,19 +2514,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -2601,19 +2534,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
         <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -2621,19 +2554,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -2641,19 +2574,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" t="s">
         <v>64</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>68</v>
-      </c>
-      <c r="F14" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -2661,19 +2594,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -2681,19 +2614,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" t="s">
         <v>37</v>
       </c>
-      <c r="D16" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" t="s">
-        <v>40</v>
-      </c>
       <c r="F16" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -2701,19 +2634,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E17" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F17" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -2721,19 +2654,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F18" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2761,13 +2694,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>28</v>
@@ -2784,19 +2717,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="E2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2804,19 +2737,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" t="s">
         <v>116</v>
       </c>
-      <c r="D3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E3" t="s">
-        <v>121</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
@@ -2824,19 +2757,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2844,19 +2777,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2864,19 +2797,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2884,19 +2817,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2904,19 +2837,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2924,19 +2857,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{033E95A3-2D98-4856-AF58-CFB8C1409040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8A5977-1EB2-44D8-8854-A0AC4519B9F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
@@ -19,10 +19,10 @@
     <sheet name="seaNormal" sheetId="8" r:id="rId4"/>
     <sheet name="seaHard" sheetId="10" r:id="rId5"/>
     <sheet name="easy_match" sheetId="3" r:id="rId6"/>
-    <sheet name="easy_classify" sheetId="4" r:id="rId7"/>
-    <sheet name="easy_card" sheetId="5" r:id="rId8"/>
-    <sheet name="easy_cloze" sheetId="7" r:id="rId9"/>
-    <sheet name="easy_sorting" sheetId="11" r:id="rId10"/>
+    <sheet name="classify" sheetId="4" r:id="rId7"/>
+    <sheet name="card" sheetId="5" r:id="rId8"/>
+    <sheet name="cloze" sheetId="7" r:id="rId9"/>
+    <sheet name="sorting" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\f\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B55DA1-7824-4F97-9362-C1F43608EC54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52705E91-595B-4662-AAF9-F43D84BA76E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
@@ -197,10 +197,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>images/s1.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>images/s2.jpg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -658,6 +654,10 @@
   </si>
   <si>
     <t>恐懼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/class.jpg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1044,7 +1044,7 @@
         <v>33</v>
       </c>
       <c r="B1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -1053,7 +1053,7 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -1064,10 +1064,10 @@
         <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E2">
         <v>200</v>
@@ -1078,13 +1078,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E3">
         <v>150</v>
@@ -1095,13 +1095,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" t="s">
         <v>51</v>
-      </c>
-      <c r="C4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" t="s">
-        <v>52</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -1115,10 +1115,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>164</v>
       </c>
       <c r="E5">
         <v>50</v>
@@ -1132,10 +1132,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>164</v>
       </c>
       <c r="E6">
         <v>300</v>
@@ -1194,13 +1194,13 @@
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1211,16 +1211,16 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
         <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1231,16 +1231,16 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
         <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1407,13 +1407,13 @@
         <v>33</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>28</v>
@@ -1427,10 +1427,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>151</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>152</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -1441,10 +1441,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>154</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -1455,10 +1455,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>156</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -1469,10 +1469,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>158</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -1483,10 +1483,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>160</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -1497,10 +1497,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>161</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>162</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -1511,10 +1511,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>164</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -1562,16 +1562,16 @@
         <v>45</v>
       </c>
       <c r="C2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" t="s">
         <v>60</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>61</v>
       </c>
-      <c r="E2" t="s">
-        <v>62</v>
-      </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1582,16 +1582,16 @@
         <v>45</v>
       </c>
       <c r="C3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" t="s">
         <v>63</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>64</v>
       </c>
-      <c r="E3" t="s">
-        <v>65</v>
-      </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1602,16 +1602,16 @@
         <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1622,16 +1622,16 @@
         <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1642,16 +1642,16 @@
         <v>45</v>
       </c>
       <c r="C6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" t="s">
         <v>68</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>69</v>
       </c>
-      <c r="E6" t="s">
-        <v>70</v>
-      </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1831,10 +1831,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1842,10 +1842,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" t="s">
         <v>76</v>
-      </c>
-      <c r="C3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1853,10 +1853,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" t="s">
         <v>78</v>
-      </c>
-      <c r="C4" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1864,10 +1864,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" t="s">
         <v>80</v>
-      </c>
-      <c r="C5" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1875,10 +1875,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" t="s">
         <v>82</v>
-      </c>
-      <c r="C6" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1886,10 +1886,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" t="s">
         <v>84</v>
-      </c>
-      <c r="C7" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1897,10 +1897,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" t="s">
         <v>86</v>
-      </c>
-      <c r="C8" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1908,10 +1908,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1919,10 +1919,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" t="s">
         <v>89</v>
-      </c>
-      <c r="C10" t="s">
-        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1971,19 +1971,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -1991,19 +1991,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
@@ -2011,19 +2011,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2031,19 +2031,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="C5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2051,19 +2051,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2071,19 +2071,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2091,19 +2091,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2111,16 +2111,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>46</v>
@@ -2170,16 +2170,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" t="s">
         <v>105</v>
       </c>
-      <c r="E2" t="s">
-        <v>106</v>
-      </c>
       <c r="F2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -2187,16 +2187,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" t="s">
         <v>101</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>102</v>
-      </c>
-      <c r="F3" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -2204,16 +2204,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" t="s">
         <v>109</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>110</v>
-      </c>
-      <c r="F4" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -2221,16 +2221,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" t="s">
         <v>113</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>114</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>115</v>
-      </c>
-      <c r="F5" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -2238,16 +2238,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" t="s">
         <v>117</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>118</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>119</v>
-      </c>
-      <c r="F6" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -2255,16 +2255,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D7" t="s">
         <v>121</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>122</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>123</v>
-      </c>
-      <c r="F7" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -2272,16 +2272,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D8" t="s">
         <v>125</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>126</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>127</v>
-      </c>
-      <c r="F8" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -2289,16 +2289,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" t="s">
         <v>129</v>
       </c>
-      <c r="E9" t="s">
-        <v>130</v>
-      </c>
       <c r="F9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -2306,16 +2306,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
+        <v>131</v>
+      </c>
+      <c r="D10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E10" t="s">
+        <v>133</v>
+      </c>
+      <c r="F10" t="s">
         <v>132</v>
-      </c>
-      <c r="D10" t="s">
-        <v>135</v>
-      </c>
-      <c r="E10" t="s">
-        <v>134</v>
-      </c>
-      <c r="F10" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -2323,16 +2323,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D11" t="s">
         <v>137</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
+        <v>139</v>
+      </c>
+      <c r="F11" t="s">
         <v>138</v>
-      </c>
-      <c r="E11" t="s">
-        <v>140</v>
-      </c>
-      <c r="F11" t="s">
-        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52705E91-595B-4662-AAF9-F43D84BA76E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5BC9115-B584-4226-95CF-D3BF77594FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="166">
   <si>
     <t>active_workSheet</t>
   </si>
@@ -658,6 +658,10 @@
   </si>
   <si>
     <t>images/class.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>match</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1030,7 +1034,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.88671875" customWidth="1"/>
@@ -1064,7 +1068,7 @@
         <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="D2" t="s">
         <v>145</v>
@@ -1081,7 +1085,7 @@
         <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D3" t="s">
         <v>48</v>
@@ -1132,13 +1136,30 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
         <v>164</v>
       </c>
       <c r="E6">
         <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E7">
+        <v>301</v>
       </c>
     </row>
   </sheetData>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5BC9115-B584-4226-95CF-D3BF77594FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7B6BB9-2153-45B2-8310-49EFE0784F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
     <sheet name="editButton" sheetId="2" r:id="rId2"/>
     <sheet name="match" sheetId="12" r:id="rId3"/>
-    <sheet name="seaCard" sheetId="9" r:id="rId4"/>
-    <sheet name="seaClassify" sheetId="8" r:id="rId5"/>
-    <sheet name="match_img" sheetId="10" r:id="rId6"/>
+    <sheet name="match_img" sheetId="10" r:id="rId4"/>
+    <sheet name="seaCard" sheetId="9" r:id="rId5"/>
+    <sheet name="seaClassify" sheetId="8" r:id="rId6"/>
     <sheet name="cloze" sheetId="7" r:id="rId7"/>
     <sheet name="sorting" sheetId="11" r:id="rId8"/>
+    <sheet name="工作表2" sheetId="14" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -599,10 +600,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>seaClassify</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>seaCard</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -662,6 +659,10 @@
   </si>
   <si>
     <t>match</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作表2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1038,8 +1039,8 @@
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17.6640625" customWidth="1"/>
-    <col min="4" max="4" width="37.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
     <col min="5" max="5" width="15.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1068,7 +1069,7 @@
         <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D2" t="s">
         <v>145</v>
@@ -1102,7 +1103,7 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D4" t="s">
         <v>51</v>
@@ -1122,7 +1123,7 @@
         <v>146</v>
       </c>
       <c r="D5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E5">
         <v>50</v>
@@ -1139,7 +1140,7 @@
         <v>140</v>
       </c>
       <c r="D6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E6">
         <v>300</v>
@@ -1153,10 +1154,10 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="D7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E7">
         <v>301</v>
@@ -1434,7 +1435,7 @@
         <v>35</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>28</v>
@@ -1448,10 +1449,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>151</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -1462,10 +1463,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>152</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>153</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -1476,10 +1477,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>155</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -1490,10 +1491,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>156</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>157</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -1504,10 +1505,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>158</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>159</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -1518,10 +1519,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>160</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>161</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -1532,10 +1533,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>163</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -1548,276 +1549,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C56893E2-0E61-4A70-8A6A-D196BA3A4361}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="45" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99363D15-D833-40CD-9C50-EF07E30035FE}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="35.33203125" customWidth="1"/>
-    <col min="3" max="3" width="37.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF84F167-113E-47C5-9256-2868DC9B612C}">
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
@@ -1950,6 +1681,276 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C56893E2-0E61-4A70-8A6A-D196BA3A4361}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="45" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99363D15-D833-40CD-9C50-EF07E30035FE}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="35.33203125" customWidth="1"/>
+    <col min="3" max="3" width="37.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2361,4 +2362,14 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D53664AE-7C50-40C4-9C11-8C9852DE56A1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7B6BB9-2153-45B2-8310-49EFE0784F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB8DB10-6E5D-47F2-97C7-9F10FFCCC0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
@@ -658,11 +658,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>match</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>工作表2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seaClassify</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1069,7 +1069,7 @@
         <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="D2" t="s">
         <v>145</v>
@@ -1086,7 +1086,7 @@
         <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="D3" t="s">
         <v>48</v>
@@ -1154,7 +1154,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D7" t="s">
         <v>163</v>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB8DB10-6E5D-47F2-97C7-9F10FFCCC0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB07AFE-5EB1-4427-89E3-5F272EC45254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="166">
   <si>
     <t>active_workSheet</t>
   </si>
@@ -2172,7 +2172,7 @@
         <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>141</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>35</v>
@@ -2191,6 +2191,9 @@
       <c r="A2">
         <v>1</v>
       </c>
+      <c r="B2" t="s">
+        <v>90</v>
+      </c>
       <c r="C2" t="s">
         <v>107</v>
       </c>
@@ -2208,6 +2211,9 @@
       <c r="A3">
         <v>2</v>
       </c>
+      <c r="B3" t="s">
+        <v>90</v>
+      </c>
       <c r="C3" t="s">
         <v>111</v>
       </c>
@@ -2225,6 +2231,9 @@
       <c r="A4">
         <v>3</v>
       </c>
+      <c r="B4" t="s">
+        <v>90</v>
+      </c>
       <c r="C4" t="s">
         <v>106</v>
       </c>
@@ -2242,6 +2251,9 @@
       <c r="A5">
         <v>4</v>
       </c>
+      <c r="B5" t="s">
+        <v>90</v>
+      </c>
       <c r="C5" t="s">
         <v>112</v>
       </c>
@@ -2259,6 +2271,9 @@
       <c r="A6">
         <v>5</v>
       </c>
+      <c r="B6" t="s">
+        <v>90</v>
+      </c>
       <c r="C6" t="s">
         <v>116</v>
       </c>
@@ -2276,6 +2291,9 @@
       <c r="A7">
         <v>6</v>
       </c>
+      <c r="B7" t="s">
+        <v>90</v>
+      </c>
       <c r="C7" t="s">
         <v>120</v>
       </c>
@@ -2293,6 +2311,9 @@
       <c r="A8">
         <v>7</v>
       </c>
+      <c r="B8" t="s">
+        <v>90</v>
+      </c>
       <c r="C8" t="s">
         <v>124</v>
       </c>
@@ -2310,6 +2331,9 @@
       <c r="A9">
         <v>8</v>
       </c>
+      <c r="B9" t="s">
+        <v>90</v>
+      </c>
       <c r="C9" t="s">
         <v>130</v>
       </c>
@@ -2327,6 +2351,9 @@
       <c r="A10">
         <v>9</v>
       </c>
+      <c r="B10" t="s">
+        <v>90</v>
+      </c>
       <c r="C10" t="s">
         <v>131</v>
       </c>
@@ -2343,6 +2370,9 @@
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>90</v>
       </c>
       <c r="C11" t="s">
         <v>136</v>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB07AFE-5EB1-4427-89E3-5F272EC45254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85605C00-DFB8-4398-AFA1-9E30626E0694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
@@ -580,10 +580,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>match_img</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>game_playtime</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -663,6 +659,10 @@
   </si>
   <si>
     <t>seaClassify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>match</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1049,7 +1049,7 @@
         <v>33</v>
       </c>
       <c r="B1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -1058,7 +1058,7 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -1069,10 +1069,10 @@
         <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E2">
         <v>200</v>
@@ -1086,7 +1086,7 @@
         <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="D3" t="s">
         <v>48</v>
@@ -1103,7 +1103,7 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D4" t="s">
         <v>51</v>
@@ -1120,10 +1120,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="D5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E5">
         <v>50</v>
@@ -1137,10 +1137,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="D6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E6">
         <v>300</v>
@@ -1154,10 +1154,10 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E7">
         <v>301</v>
@@ -1435,7 +1435,7 @@
         <v>35</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>28</v>
@@ -1449,10 +1449,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>150</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -1463,10 +1463,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>151</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>152</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -1477,10 +1477,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>154</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -1491,10 +1491,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>156</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -1505,10 +1505,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>157</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>158</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -1519,10 +1519,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>160</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -1533,10 +1533,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>161</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>162</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85605C00-DFB8-4398-AFA1-9E30626E0694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3831E6-9D86-41FA-977A-8A503CDBF3AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="164">
   <si>
     <t>active_workSheet</t>
   </si>
@@ -231,12 +231,6 @@
 Remember, we only have one Earth and one ocean.
 If we all do a little, we can protect our beautiful planet and our ocean friends together.</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>clownfish</t>
-  </si>
-  <si>
-    <t>dolphin</t>
   </si>
   <si>
     <t>flyingfish</t>
@@ -1049,7 +1043,7 @@
         <v>33</v>
       </c>
       <c r="B1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -1058,7 +1052,7 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -1069,10 +1063,10 @@
         <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E2">
         <v>200</v>
@@ -1086,7 +1080,7 @@
         <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D3" t="s">
         <v>48</v>
@@ -1103,7 +1097,7 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D4" t="s">
         <v>51</v>
@@ -1120,10 +1114,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E5">
         <v>50</v>
@@ -1137,10 +1131,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E6">
         <v>300</v>
@@ -1154,10 +1148,10 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E7">
         <v>301</v>
@@ -1233,16 +1227,16 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
         <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1253,16 +1247,16 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
         <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1429,13 +1423,13 @@
         <v>33</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>28</v>
@@ -1449,10 +1443,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -1463,10 +1457,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -1477,10 +1471,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -1491,10 +1485,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -1505,10 +1499,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -1519,10 +1513,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -1533,10 +1527,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -1583,10 +1577,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" t="s">
         <v>72</v>
-      </c>
-      <c r="C2" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1594,10 +1588,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1605,10 +1599,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1616,10 +1610,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1627,10 +1621,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1638,10 +1632,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1649,10 +1643,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1660,10 +1654,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1671,10 +1665,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1720,16 +1714,16 @@
         <v>45</v>
       </c>
       <c r="C2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" t="s">
         <v>59</v>
       </c>
-      <c r="D2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" t="s">
-        <v>61</v>
-      </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1740,16 +1734,16 @@
         <v>45</v>
       </c>
       <c r="C3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" t="s">
         <v>62</v>
       </c>
-      <c r="D3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" t="s">
-        <v>64</v>
-      </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1760,16 +1754,16 @@
         <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1780,16 +1774,16 @@
         <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1800,16 +1794,16 @@
         <v>45</v>
       </c>
       <c r="C6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" t="s">
         <v>67</v>
       </c>
-      <c r="D6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" t="s">
-        <v>69</v>
-      </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1833,7 +1827,7 @@
         <v>33</v>
       </c>
       <c r="B1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C1" t="s">
         <v>35</v>
@@ -1993,19 +1987,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" t="s">
         <v>62</v>
       </c>
-      <c r="D2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E2" t="s">
-        <v>64</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2013,19 +2007,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
@@ -2033,19 +2027,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2053,19 +2047,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" t="s">
         <v>67</v>
       </c>
-      <c r="D5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" t="s">
-        <v>69</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2073,19 +2067,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2093,19 +2087,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2113,19 +2107,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2133,16 +2127,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>46</v>
@@ -2172,7 +2166,7 @@
         <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>35</v>
@@ -2192,19 +2186,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -2212,19 +2206,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3" t="s">
         <v>100</v>
-      </c>
-      <c r="E3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F3" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -2232,19 +2226,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" t="s">
         <v>106</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F4" t="s">
         <v>108</v>
-      </c>
-      <c r="E4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F4" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -2252,19 +2246,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" t="s">
         <v>112</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>113</v>
-      </c>
-      <c r="E5" t="s">
-        <v>114</v>
-      </c>
-      <c r="F5" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -2272,19 +2266,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E6" t="s">
         <v>116</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>117</v>
-      </c>
-      <c r="E6" t="s">
-        <v>118</v>
-      </c>
-      <c r="F6" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -2292,19 +2286,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" t="s">
         <v>120</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>121</v>
-      </c>
-      <c r="E7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F7" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -2312,19 +2306,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E8" t="s">
         <v>124</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>125</v>
-      </c>
-      <c r="E8" t="s">
-        <v>126</v>
-      </c>
-      <c r="F8" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -2332,19 +2326,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -2352,19 +2346,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
+        <v>129</v>
+      </c>
+      <c r="D10" t="s">
+        <v>132</v>
+      </c>
+      <c r="E10" t="s">
         <v>131</v>
       </c>
-      <c r="D10" t="s">
-        <v>134</v>
-      </c>
-      <c r="E10" t="s">
-        <v>133</v>
-      </c>
       <c r="F10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -2372,19 +2366,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D11" t="s">
+        <v>135</v>
+      </c>
+      <c r="E11" t="s">
+        <v>137</v>
+      </c>
+      <c r="F11" t="s">
         <v>136</v>
-      </c>
-      <c r="D11" t="s">
-        <v>137</v>
-      </c>
-      <c r="E11" t="s">
-        <v>139</v>
-      </c>
-      <c r="F11" t="s">
-        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3831E6-9D86-41FA-977A-8A503CDBF3AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3801ACCF-F468-4B30-ADD9-8EF30D8D0CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1734,7 +1734,7 @@
         <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
         <v>61</v>
@@ -1743,7 +1743,7 @@
         <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3801ACCF-F468-4B30-ADD9-8EF30D8D0CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69942470-132F-4E7D-B5FD-6701EBC3AD7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69942470-132F-4E7D-B5FD-6701EBC3AD7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB5D9AA-A694-431B-B7EA-7E4DDFA2A75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
@@ -1063,7 +1063,7 @@
         <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D2" t="s">
         <v>142</v>
@@ -1097,7 +1097,7 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D4" t="s">
         <v>51</v>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB5D9AA-A694-431B-B7EA-7E4DDFA2A75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0C90199-915E-409E-9850-FC4D5B64BC3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1063,7 +1063,7 @@
         <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D2" t="s">
         <v>142</v>
@@ -1080,7 +1080,7 @@
         <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D3" t="s">
         <v>48</v>

--- a/questionData.xlsx
+++ b/questionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0C90199-915E-409E-9850-FC4D5B64BC3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05FEE14A-16C5-49C0-A534-48D8B72DB4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
@@ -33,12 +33,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="164">
   <si>
     <t>active_workSheet</t>
-  </si>
-  <si>
-    <t>background</t>
   </si>
   <si>
     <t>Scene1</t>
@@ -657,6 +654,10 @@
   </si>
   <si>
     <t>match</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>background</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1040,19 +1041,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>1</v>
+        <v>163</v>
       </c>
       <c r="E1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -1060,13 +1061,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E2">
         <v>200</v>
@@ -1077,13 +1078,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E3">
         <v>150</v>
@@ -1094,13 +1095,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" t="s">
         <v>50</v>
-      </c>
-      <c r="C4" t="s">
-        <v>144</v>
-      </c>
-      <c r="D4" t="s">
-        <v>51</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -1111,13 +1112,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E5">
         <v>50</v>
@@ -1128,13 +1129,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E6">
         <v>300</v>
@@ -1145,24 +1146,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E7">
         <v>301</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="1"/>
+  <protectedRanges>
+    <protectedRange sqref="A2:XFD1048576" name="範圍1"/>
+  </protectedRanges>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="C1:D1" numberStoredAsText="1"/>
+    <ignoredError sqref="C1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1181,22 +1186,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
@@ -1204,19 +1209,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="E2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1224,19 +1229,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1244,19 +1249,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1264,19 +1269,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1284,19 +1289,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="81" x14ac:dyDescent="0.3">
@@ -1304,19 +1309,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1324,19 +1329,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
         <v>18</v>
       </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" t="s">
-        <v>19</v>
-      </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1344,19 +1349,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
         <v>31</v>
       </c>
-      <c r="E9" t="s">
-        <v>32</v>
-      </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1364,19 +1369,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
         <v>21</v>
       </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" t="s">
-        <v>22</v>
-      </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1384,19 +1389,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
         <v>23</v>
       </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>24</v>
-      </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1420,22 +1425,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1443,10 +1448,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>147</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -1457,10 +1462,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>149</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -1471,10 +1476,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>151</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -1485,10 +1490,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>152</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>153</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -1499,10 +1504,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>154</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>155</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -1513,10 +1518,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>156</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>157</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -1527,10 +1532,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>159</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -1554,22 +1559,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1577,10 +1582,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1588,10 +1593,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" t="s">
         <v>73</v>
-      </c>
-      <c r="C3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1599,10 +1604,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" t="s">
         <v>75</v>
-      </c>
-      <c r="C4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1610,10 +1615,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" t="s">
         <v>77</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1621,10 +1626,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" t="s">
         <v>79</v>
-      </c>
-      <c r="C6" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1632,10 +1637,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" t="s">
         <v>81</v>
-      </c>
-      <c r="C7" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1643,10 +1648,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" t="s">
         <v>83</v>
-      </c>
-      <c r="C8" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1654,10 +1659,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1665,10 +1670,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" t="s">
         <v>86</v>
-      </c>
-      <c r="C10" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1688,22 +1693,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1711,19 +1716,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
         <v>57</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>58</v>
       </c>
-      <c r="E2" t="s">
-        <v>59</v>
-      </c>
       <c r="F2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1731,19 +1736,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" t="s">
         <v>60</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>61</v>
       </c>
-      <c r="E3" t="s">
-        <v>62</v>
-      </c>
       <c r="F3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1751,19 +1756,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1771,19 +1776,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1791,19 +1796,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" t="s">
         <v>65</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>66</v>
       </c>
-      <c r="E6" t="s">
-        <v>67</v>
-      </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1824,22 +1829,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1847,10 +1852,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1858,10 +1863,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1869,10 +1874,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1880,10 +1885,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1891,10 +1896,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1902,10 +1907,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1913,10 +1918,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1924,10 +1929,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1935,10 +1940,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1964,22 +1969,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -1987,19 +1992,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2007,19 +2012,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="48.6" x14ac:dyDescent="0.3">
@@ -2027,19 +2032,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2047,19 +2052,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="C5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2067,19 +2072,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2087,19 +2092,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2107,19 +2112,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -2127,19 +2132,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -2163,22 +2168,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -2186,19 +2191,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2" t="s">
         <v>102</v>
       </c>
-      <c r="E2" t="s">
-        <v>103</v>
-      </c>
       <c r="F2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -2206,19 +2211,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" t="s">
         <v>98</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -2226,19 +2231,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" t="s">
         <v>106</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>107</v>
-      </c>
-      <c r="F4" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -2246,19 +2251,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" t="s">
         <v>110</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>111</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>112</v>
-      </c>
-      <c r="F5" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -2266,19 +2271,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" t="s">
         <v>114</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>115</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>116</v>
-      </c>
-      <c r="F6" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -2286,19 +2291,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" t="s">
         <v>118</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>119</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>120</v>
-      </c>
-      <c r="F7" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -2306,19 +2311,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" t="s">
         <v>122</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>123</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>124</v>
-      </c>
-      <c r="F8" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -2326,19 +2331,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E9" t="s">
         <v>126</v>
       </c>
-      <c r="E9" t="s">
-        <v>127</v>
-      </c>
       <c r="F9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -2346,19 +2351,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" t="s">
+        <v>131</v>
+      </c>
+      <c r="E10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10" t="s">
         <v>129</v>
-      </c>
-      <c r="D10" t="s">
-        <v>132</v>
-      </c>
-      <c r="E10" t="s">
-        <v>131</v>
-      </c>
-      <c r="F10" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -2366,19 +2371,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
+        <v>133</v>
+      </c>
+      <c r="D11" t="s">
         <v>134</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F11" t="s">
         <v>135</v>
-      </c>
-      <c r="E11" t="s">
-        <v>137</v>
-      </c>
-      <c r="F11" t="s">
-        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -2390,9 +2395,30 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D53664AE-7C50-40C4-9C11-8C9852DE56A1}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
